--- a/functional_tests/ZBIO-5213/ZBIO-5213.xlsx
+++ b/functional_tests/ZBIO-5213/ZBIO-5213.xlsx
@@ -4,22 +4,16 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Test Scenarios" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="155">
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>description</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="149">
+  <si>
+    <t>scenario</t>
   </si>
   <si>
     <t>testId</t>
@@ -37,13 +31,7 @@
     <t>expectedResult</t>
   </si>
   <si>
-    <t>functional</t>
-  </si>
-  <si>
-    <t>[State Transition] Valid Transition from 'Current' to 'Payment Due Soon'</t>
-  </si>
-  <si>
-    <t>Verify that an account with an upcoming due date correctly transitions to the 'Payment Due Soon' state and triggers the 'Credit Card Due Reminder' notification.</t>
+    <t>&lt;[State Transition] Valid Transition from 'Current' to 'Payment Due Soon'-Verify that an account with an upcoming due date correctly transitions to the 'Payment Due Soon' state and triggers the 'Credit Card Due Reminder' notification.&gt;</t>
   </si>
   <si>
     <t>TC-ST-001</t>
@@ -76,10 +64,7 @@
     <t>A 'Credit Card Due Reminder' is successfully sent via both email and SMS. The notification content is accurate and contains only the last 4 digits of the card number. The account status in the core system is updated to 'Payment Due Soon'.</t>
   </si>
   <si>
-    <t>[State Transition] Valid Transition from 'Payment Due Soon' to 'Overdue'</t>
-  </si>
-  <si>
-    <t>Verify that an account in the 'Payment Due Soon' state, for which no payment is received by the due date, correctly transitions to 'Overdue' and triggers the 'Overdue Balance Alert'.</t>
+    <t>&lt;[State Transition] Valid Transition from 'Payment Due Soon' to 'Overdue'-Verify that an account in the 'Payment Due Soon' state, for which no payment is received by the due date, correctly transitions to 'Overdue' and triggers the 'Overdue Balance Alert'.&gt;</t>
   </si>
   <si>
     <t>TC-ST-002</t>
@@ -111,10 +96,7 @@
     <t>An 'Overdue Balance Alert' is sent with accurate, compliant content. The account status is updated to 'Overdue', and any applicable late fees are posted to the account.</t>
   </si>
   <si>
-    <t>[State Transition] Valid Transition from 'Overdue' to 'Significantly Delinquent/In Collections'</t>
-  </si>
-  <si>
-    <t>Verify that an 'Overdue' account correctly transitions to 'In Collections' after a specified period of delinquency (e.g., 30 days) and triggers the formal 'Collection Notification'.</t>
+    <t>&lt;[State Transition] Valid Transition from 'Overdue' to 'Significantly Delinquent/In Collections'-Verify that an 'Overdue' account correctly transitions to 'In Collections' after a specified period of delinquency (e.g., 30 days) and triggers the formal 'Collection Notification'.&gt;</t>
   </si>
   <si>
     <t>TC-ST-003</t>
@@ -145,10 +127,7 @@
     <t>A formal 'Collection Notification' is sent. The notification accurately details the total amount owed, including an itemization of all charges. The account status is correctly updated to 'In Collections'.</t>
   </si>
   <si>
-    <t>[State Transition] Invalid Transition from 'Current' to 'In Collections'</t>
-  </si>
-  <si>
-    <t>Verify that the system prevents an account from transitioning directly from 'Current' to 'In Collections', and that no collection notification is sent.</t>
+    <t>&lt;[State Transition] Invalid Transition from 'Current' to 'In Collections'-Verify that the system prevents an account from transitioning directly from 'Current' to 'In Collections', and that no collection notification is sent.&gt;</t>
   </si>
   <si>
     <t>TC-ST-004</t>
@@ -176,10 +155,92 @@
     <t>The system rejects the invalid state transition. No collection-related notifications are sent for the account. The account's status remains 'Current'.</t>
   </si>
   <si>
-    <t>[Decision Table] Notification Suppression for Customer Opt-Out</t>
-  </si>
-  <si>
-    <t>Verify that no notifications are sent for an account that meets all delinquency criteria but the customer has opted out of communications.</t>
+    <t>&lt;[State Transition] 'In Collections' Account Receives 'Payment Plan Proposal'-Verify that a delinquent account is correctly offered a payment plan and the corresponding notification is sent.&gt;</t>
+  </si>
+  <si>
+    <t>TC-ST-005</t>
+  </si>
+  <si>
+    <t>This test validates the system's ability to identify eligible candidates for a payment plan, generate a proposal, and communicate it to the customer. This is a de-escalation path within the collections process.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. An account is in the 'In Collections' state.
+2. The account meets internal criteria for a payment plan offer (e.g., delinquency age between 30-60 days, no prior broken plans).
+3. The customer is opted-in for notifications.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set up an account with PAN '...5551' that is 45 days past due and has a status of 'In Collections'.
+2. Ensure the account balance is $1800.
+3. Execute the daily collections strategy job.
+4. Verify the system logic identifies the account as eligible for a payment plan.
+5. Query the notification service logs for a 'Payment Plan Proposal' sent to the customer.
+6. Retrieve the sent email.
+7. Verify the email subject line clearly states it's a payment plan offer and includes the masked PAN '...5551'.
+8. Verify the email body details the total amount owed ($1800) and presents a clear repayment schedule (e.g., 6 monthly payments of $310).
+9. Verify the email includes instructions on how to accept the plan.
+10. Query the account's sub-status in the core system and confirm it has been updated to 'In Collections - Plan Offered'.</t>
+  </si>
+  <si>
+    <t>A 'Payment Plan Proposal' notification is sent with accurate financial details and a clear call to action. The account's status is updated to reflect that a plan has been offered.</t>
+  </si>
+  <si>
+    <t>&lt;[State Transition] 'In Collections' Account Escalated to 'Collection Agency'-Verify that an account that remains unpaid after a certain period is correctly assigned to an external collection agency.&gt;</t>
+  </si>
+  <si>
+    <t>TC-ST-006</t>
+  </si>
+  <si>
+    <t>This test validates the final internal escalation step before potential legal action. It ensures the account status is updated and a notification of agency involvement is sent to the customer.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. An account is in the 'In Collections' state.
+2. The account has been delinquent for a specified period (e.g., 90 days).
+3. The customer has not accepted any payment plans or made significant payments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set up an account with PAN '...5552' that is 90 days past due and has a status of 'In Collections'.
+2. Execute the daily collections strategy job.
+3. Verify the system logic flags the account for transfer to a collection agency.
+4. Query the notification service logs for a 'Notice of Collection Agency Assignment' sent to the customer.
+5. Retrieve the sent email.
+6. Verify the email informs the customer that their debt has been assigned to a specific agency and provides the agency's contact information.
+7. Verify the email includes the masked PAN '...5552' for reference.
+8. Query the account's status in the core system and confirm it has transitioned to 'Assigned to Collection Agency'.
+9. Verify that an outbound data file/API call is generated for the collection agency containing the necessary (and securely handled) account details, including the masked PAN.</t>
+  </si>
+  <si>
+    <t>The account status is updated to 'Assigned to Collection Agency', a compliant notification is sent to the customer, and the necessary data is prepared for the external agency.</t>
+  </si>
+  <si>
+    <t>&lt;[State Transition] Account Escalated to 'Legal Action'-Verify that in extreme cases, an account is correctly flagged for legal action and the appropriate formal notification is generated.&gt;</t>
+  </si>
+  <si>
+    <t>TC-ST-007</t>
+  </si>
+  <si>
+    <t>This test validates the system's capability to handle the most severe delinquency cases, ensuring the account is correctly flagged and documented for legal proceedings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. An account is with a collection agency.
+2. The delinquency has aged beyond a certain threshold (e.g., 180 days) with no resolution.
+3. The balance exceeds a minimum amount required for legal action.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set up an account with PAN '...5553' that is 180 days past due and has a status of 'Assigned to Collection Agency'.
+2. Ensure the balance is significant (e.g., &gt; $5000).
+3. Execute the monthly/quarterly legal review batch job.
+4. Verify the system logic identifies the account as a candidate for legal action.
+5. Query the notification service logs for a 'Notice of Intent for Legal Action' sent to the customer (if required by policy).
+6. Retrieve the sent formal letter/email.
+7. Verify the communication uses formal legal language, details the outstanding debt, and mentions the last 4 digits of the card '...5553'.
+8. Query the account's status in the core system and confirm it has transitioned to 'Legal Action Pending' or a similar state.
+9. Verify that the account is added to a report or queue for the bank's legal department.</t>
+  </si>
+  <si>
+    <t>The account status is updated to 'Legal Action Pending', a formal notification is sent (if applicable), and the account is flagged for review by the legal team.</t>
+  </si>
+  <si>
+    <t>&lt;[Decision Table] Notification Suppression for Customer Opt-Out-Verify that no notifications are sent for an account that meets all delinquency criteria but the customer has opted out of communications.&gt;</t>
   </si>
   <si>
     <t>TC-DT-001</t>
@@ -207,10 +268,7 @@
     <t>The account status correctly updates to 'Overdue', but no notifications are sent to the customer. The system logs the suppression event internally.</t>
   </si>
   <si>
-    <t>[Decision Table] Notification Suppression for 'Bankrupt' Account Flag</t>
-  </si>
-  <si>
-    <t>Verify that all collection-related notifications are suppressed for an account that is flagged as being in bankruptcy, regardless of its delinquency status.</t>
+    <t>&lt;[Decision Table] Notification Suppression for 'Bankrupt' Account Flag-Verify that all collection-related notifications are suppressed for an account that is flagged as being in bankruptcy, regardless of its delinquency status.&gt;</t>
   </si>
   <si>
     <t>TC-DT-002</t>
@@ -238,10 +296,7 @@
     <t>No collection notifications of any kind are sent to the customer. The system correctly suppresses communication based on the 'Bankrupt' flag.</t>
   </si>
   <si>
-    <t>[Decision Table] Notification Suppression for Zero Balance Account</t>
-  </si>
-  <si>
-    <t>Verify that no 'Overdue Balance Alert' is sent if an account is past its due date but has a zero balance.</t>
+    <t>&lt;[Decision Table] Notification Suppression for Zero Balance Account-Verify that no 'Overdue Balance Alert' is sent if an account is past its due date but has a zero balance.&gt;</t>
   </si>
   <si>
     <t>TC-DT-003</t>
@@ -269,10 +324,7 @@
     <t>No notifications are sent for the account. The system correctly identifies that there is no overdue balance to collect, despite the due date having passed.</t>
   </si>
   <si>
-    <t>[Boundary Value] 'Due Reminder' Trigger on First Day of Window</t>
-  </si>
-  <si>
-    <t>Verify that the 'Credit Card Due Reminder' is sent exactly on the first day of the notification window (e.g., T-minus 3 days to due date).</t>
+    <t>&lt;[Boundary Value] 'Due Reminder' Trigger on First Day of Window-Verify that the 'Credit Card Due Reminder' is sent exactly on the first day of the notification window (e.g., T-minus 3 days to due date).&gt;</t>
   </si>
   <si>
     <t>TC-BVA-001</t>
@@ -300,10 +352,7 @@
     <t>The reminder notification is sent only for the account that is exactly 3 days away from its due date. The account that is 4 days away does not receive a notification.</t>
   </si>
   <si>
-    <t>[Boundary Value] 'Overdue Alert' Trigger Immediately After Midnight</t>
-  </si>
-  <si>
-    <t>Verify that the 'Overdue Balance Alert' is triggered when the system clock ticks over to midnight, making the account exactly 1 day overdue.</t>
+    <t>&lt;[Boundary Value] 'Overdue Alert' Trigger Immediately After Midnight-Verify that the 'Overdue Balance Alert' is triggered when the system clock ticks over to midnight, making the account exactly 1 day overdue.&gt;</t>
   </si>
   <si>
     <t>TC-BVA-002</t>
@@ -331,10 +380,7 @@
     <t>The 'Overdue Balance Alert' is not sent on the due date itself but is sent immediately after the date changes to the next day (1 day overdue).</t>
   </si>
   <si>
-    <t>[Boundary Value] 'Collection Notification' Trigger on Exact Delinquency Day</t>
-  </si>
-  <si>
-    <t>Verify the 'Collection Notification' is sent on the exact day the account meets the 'significantly delinquent' threshold (e.g., 30 days past due) and not the day before.</t>
+    <t>&lt;[Boundary Value] 'Collection Notification' Trigger on Exact Delinquency Day-Verify the 'Collection Notification' is sent on the exact day the account meets the 'significantly delinquent' threshold (e.g., 30 days past due) and not the day before.&gt;</t>
   </si>
   <si>
     <t>TC-BVA-003</t>
@@ -364,10 +410,7 @@
     <t>The 'Collection Notification' is suppressed on day 29 but is successfully triggered and sent on day 30, the exact boundary for significant delinquency.</t>
   </si>
   <si>
-    <t>[Security] PII Masking Verification in 'Due Reminder' Email</t>
-  </si>
-  <si>
-    <t>Rigorously verify that only the last 4 digits of the PAN are present in the 'Credit Card Due Reminder' email and the full PAN is never exposed.</t>
+    <t>&lt;[Security] PII Masking Verification in 'Due Reminder' Email-Rigorously verify that only the last 4 digits of the PAN are present in the 'Credit Card Due Reminder' email and the full PAN is never exposed.&gt;</t>
   </si>
   <si>
     <t>TC-SEC-001</t>
@@ -396,10 +439,7 @@
     <t>The full PAN is absent from the API payload and all parts of the final email notification. Only the correctly masked last 4 digits are displayed.</t>
   </si>
   <si>
-    <t>[Security] PII Masking Verification in 'Overdue Alert' SMS</t>
-  </si>
-  <si>
-    <t>Verify that only the last 4 digits of the PAN are present in the 'Overdue Balance Alert' SMS message.</t>
+    <t>&lt;[Security] PII Masking Verification in 'Overdue Alert' SMS-Verify that only the last 4 digits of the PAN are present in the 'Overdue Balance Alert' SMS message.&gt;</t>
   </si>
   <si>
     <t>TC-SEC-002</t>
@@ -425,10 +465,7 @@
     <t>The SMS message content correctly includes the masked last 4 digits of the PAN and does not contain the full PAN.</t>
   </si>
   <si>
-    <t>[Security] PII Masking Verification in 'Collection Notification' Multi-Channel</t>
-  </si>
-  <si>
-    <t>Verify PII masking in the formal 'Collection Notification' across all potential channels (Email, SMS, Push Notification).</t>
+    <t>&lt;[Security] PII Masking Verification in 'Collection Notification' Multi-Channel-Verify PII masking in the formal 'Collection Notification' across all potential channels (Email, SMS, Push Notification).&gt;</t>
   </si>
   <si>
     <t>TC-SEC-003</t>
@@ -455,10 +492,7 @@
     <t>The PAN is correctly masked to the last 4 digits in the API payloads and final content for all three communication channels (Email, SMS, Push).</t>
   </si>
   <si>
-    <t>[Integration] Data Integrity of Financials in 'Collection Notification'</t>
-  </si>
-  <si>
-    <t>Verify that the 'amount owed' and 'additional charges' in the 'Collection Notification' perfectly match the data in the core banking ledger at the moment of generation.</t>
+    <t>&lt;[Integration] Data Integrity of Financials in 'Collection Notification'-Verify that the 'amount owed' and 'additional charges' in the 'Collection Notification' perfectly match the data in the core banking ledger at the moment of generation.&gt;</t>
   </si>
   <si>
     <t>TC-INT-001</t>
@@ -487,10 +521,7 @@
     <t>The financial figures in the 'Collection Notification' (total, principal, fees, interest) are 100% accurate and match the state of the core banking ledger.</t>
   </si>
   <si>
-    <t>[Integration] Race Condition - Payment Posted Moments Before Overdue Alert Generation</t>
-  </si>
-  <si>
-    <t>Verify that if a full payment is posted moments before the overdue notification job runs, the 'Overdue Balance Alert' is correctly suppressed.</t>
+    <t>&lt;[Integration] Race Condition - Payment Posted Moments Before Overdue Alert Generation-Verify that if a full payment is posted moments before the overdue notification job runs, the 'Overdue Balance Alert' is correctly suppressed.&gt;</t>
   </si>
   <si>
     <t>TC-INT-002</t>
@@ -518,10 +549,7 @@
     <t>The system correctly identifies the last-second payment, updates the account's status, and suppresses the 'Overdue Balance Alert'. No notification is sent.</t>
   </si>
   <si>
-    <t>[Exception] Notification Service API Unavailable</t>
-  </si>
-  <si>
-    <t>Verify the system's behavior when the external notification service API is down or returns a server error (e.g., 503 Service Unavailable).</t>
+    <t>&lt;[Exception] Notification Service API Unavailable-Verify the system's behavior when the external notification service API is down or returns a server error (e.g., 503 Service Unavailable).&gt;</t>
   </si>
   <si>
     <t>TC-EX-001</t>
@@ -550,10 +578,7 @@
     <t>The system logs the failure, marks the notification for retry without crashing the batch job, and does not lose the notification request.</t>
   </si>
   <si>
-    <t>[Exception] Invalid Customer Contact Information (Email)</t>
-  </si>
-  <si>
-    <t>Verify the system's handling of a customer with an invalidly formatted email address.</t>
+    <t>&lt;[Exception] Invalid Customer Contact Information (Email)-Verify the system's handling of a customer with an invalidly formatted email address.&gt;</t>
   </si>
   <si>
     <t>TC-EX-002</t>
@@ -581,10 +606,7 @@
     <t>The system logs the delivery failure for the invalid email address, marks the notification appropriately, and continues processing the rest of the batch successfully.</t>
   </si>
   <si>
-    <t>[Exception] Account with a Credit (Negative) Balance</t>
-  </si>
-  <si>
-    <t>Verify that no collection lifecycle notifications are sent for an account that has a credit balance, even if a 'due date' is present.</t>
+    <t>&lt;[Exception] Account with a Credit (Negative) Balance-Verify that no collection lifecycle notifications are sent for an account that has a credit balance, even if a 'due date' is present.&gt;</t>
   </si>
   <si>
     <t>TC-EX-003</t>
@@ -613,10 +635,7 @@
     <t>The system correctly identifies the credit balance and suppresses all reminder, overdue, and collection notifications for the account.</t>
   </si>
   <si>
-    <t>[End-to-End] Happy Path Full Delinquency Lifecycle</t>
-  </si>
-  <si>
-    <t>Trace a single account through the entire lifecycle: from 'Due Reminder' to 'Overdue Alert' to 'Collection Notification' without any payments.</t>
+    <t>&lt;[End-to-End] Happy Path Full Delinquency Lifecycle-Trace a single account through the entire lifecycle: from 'Due Reminder' to 'Overdue Alert' to 'Collection Notification' without any payments.&gt;</t>
   </si>
   <si>
     <t>TC-E2E-001</t>
@@ -646,10 +665,7 @@
     <t>The account correctly progresses through each state of the collection lifecycle, with the appropriate, accurate, and secure notification being sent at each defined time-based trigger.</t>
   </si>
   <si>
-    <t>[End-to-End] Lifecycle Interrupted by Full Payment</t>
-  </si>
-  <si>
-    <t>Trace an account that becomes overdue but is then paid in full, verifying that the lifecycle is halted and no further collection notices are sent.</t>
+    <t>&lt;[End-to-End] Lifecycle Interrupted by Full Payment-Trace an account that becomes overdue but is then paid in full, verifying that the lifecycle is halted and no further collection notices are sent.&gt;</t>
   </si>
   <si>
     <t>TC-E2E-002</t>
@@ -676,10 +692,7 @@
     <t>The collection lifecycle is successfully terminated upon receipt of full payment. The system does not send the 'Collection Notification' after the account balance becomes zero.</t>
   </si>
   <si>
-    <t>[End-to-End] Lifecycle Halted by 'Disputed' Account Flag</t>
-  </si>
-  <si>
-    <t>Trace an account that becomes overdue, then has a dispute flag applied, verifying that the escalation to collections is suppressed while the dispute is active.</t>
+    <t>&lt;[End-to-End] Lifecycle Halted by 'Disputed' Account Flag-Trace an account that becomes overdue, then has a dispute flag applied, verifying that the escalation to collections is suppressed while the dispute is active.&gt;</t>
   </si>
   <si>
     <t>TC-E2E-003</t>
@@ -1077,16 +1090,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="8" width="50" customWidth="1"/>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="6" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1105,557 +1117,485 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="D4" t="s">
         <v>21</v>
       </c>
-      <c r="H3" t="s">
+      <c r="E4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="F4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="C5" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
+      <c r="D5" t="s">
         <v>27</v>
       </c>
-      <c r="G4" t="s">
+      <c r="E5" t="s">
         <v>28</v>
       </c>
-      <c r="H4" t="s">
+      <c r="F5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>30</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
         <v>31</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C6" t="s">
         <v>32</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D6" t="s">
         <v>33</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E6" t="s">
         <v>34</v>
       </c>
-      <c r="G5" t="s">
+      <c r="F6" t="s">
         <v>35</v>
       </c>
-      <c r="H5" t="s">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>37</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>38</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>39</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
         <v>40</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F7" t="s">
         <v>41</v>
       </c>
-      <c r="G6" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>42</v>
       </c>
-      <c r="H6" t="s">
+      <c r="B8" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C8" t="s">
         <v>44</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D8" t="s">
         <v>45</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E8" t="s">
         <v>46</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F8" t="s">
         <v>47</v>
       </c>
-      <c r="F7" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>48</v>
       </c>
-      <c r="G7" t="s">
+      <c r="B9" t="s">
         <v>49</v>
       </c>
-      <c r="H7" t="s">
+      <c r="C9" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="D9" t="s">
         <v>51</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E9" t="s">
         <v>52</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F9" t="s">
         <v>53</v>
       </c>
-      <c r="E8" t="s">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>54</v>
       </c>
-      <c r="F8" t="s">
+      <c r="B10" t="s">
         <v>55</v>
       </c>
-      <c r="G8" t="s">
+      <c r="C10" t="s">
         <v>56</v>
       </c>
-      <c r="H8" t="s">
+      <c r="D10" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="E10" t="s">
         <v>58</v>
       </c>
-      <c r="C9" t="s">
+      <c r="F10" t="s">
         <v>59</v>
       </c>
-      <c r="D9" t="s">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>60</v>
       </c>
-      <c r="E9" t="s">
+      <c r="B11" t="s">
         <v>61</v>
       </c>
-      <c r="F9" t="s">
+      <c r="C11" t="s">
         <v>62</v>
       </c>
-      <c r="G9" t="s">
+      <c r="D11" t="s">
         <v>63</v>
       </c>
-      <c r="H9" t="s">
+      <c r="E11" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="F11" t="s">
         <v>65</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>66</v>
       </c>
-      <c r="D10" t="s">
+      <c r="B12" t="s">
         <v>67</v>
       </c>
-      <c r="E10" t="s">
+      <c r="C12" t="s">
         <v>68</v>
       </c>
-      <c r="F10" t="s">
+      <c r="D12" t="s">
         <v>69</v>
       </c>
-      <c r="G10" t="s">
+      <c r="E12" t="s">
         <v>70</v>
       </c>
-      <c r="H10" t="s">
+      <c r="F12" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>72</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B13" t="s">
         <v>73</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C13" t="s">
         <v>74</v>
       </c>
-      <c r="E11" t="s">
+      <c r="D13" t="s">
         <v>75</v>
       </c>
-      <c r="F11" t="s">
+      <c r="E13" t="s">
         <v>76</v>
       </c>
-      <c r="G11" t="s">
+      <c r="F13" t="s">
         <v>77</v>
       </c>
-      <c r="H11" t="s">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="B14" t="s">
         <v>79</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C14" t="s">
         <v>80</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D14" t="s">
         <v>81</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E14" t="s">
         <v>82</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F14" t="s">
         <v>83</v>
       </c>
-      <c r="G12" t="s">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>84</v>
       </c>
-      <c r="H12" t="s">
+      <c r="B15" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C15" t="s">
         <v>86</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D15" t="s">
         <v>87</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E15" t="s">
         <v>88</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F15" t="s">
         <v>89</v>
       </c>
-      <c r="F13" t="s">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>90</v>
       </c>
-      <c r="G13" t="s">
+      <c r="B16" t="s">
         <v>91</v>
       </c>
-      <c r="H13" t="s">
+      <c r="C16" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="D16" t="s">
         <v>93</v>
       </c>
-      <c r="C14" t="s">
+      <c r="E16" t="s">
         <v>94</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F16" t="s">
         <v>95</v>
       </c>
-      <c r="E14" t="s">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>96</v>
       </c>
-      <c r="F14" t="s">
+      <c r="B17" t="s">
         <v>97</v>
       </c>
-      <c r="G14" t="s">
+      <c r="C17" t="s">
         <v>98</v>
       </c>
-      <c r="H14" t="s">
+      <c r="D17" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="E17" t="s">
         <v>100</v>
       </c>
-      <c r="C15" t="s">
+      <c r="F17" t="s">
         <v>101</v>
       </c>
-      <c r="D15" t="s">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>102</v>
       </c>
-      <c r="E15" t="s">
+      <c r="B18" t="s">
         <v>103</v>
       </c>
-      <c r="F15" t="s">
+      <c r="C18" t="s">
         <v>104</v>
       </c>
-      <c r="G15" t="s">
+      <c r="D18" t="s">
         <v>105</v>
       </c>
-      <c r="H15" t="s">
+      <c r="E18" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="F18" t="s">
         <v>107</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>108</v>
       </c>
-      <c r="D16" t="s">
+      <c r="B19" t="s">
         <v>109</v>
       </c>
-      <c r="E16" t="s">
+      <c r="C19" t="s">
         <v>110</v>
       </c>
-      <c r="F16" t="s">
+      <c r="D19" t="s">
         <v>111</v>
       </c>
-      <c r="G16" t="s">
+      <c r="E19" t="s">
         <v>112</v>
       </c>
-      <c r="H16" t="s">
+      <c r="F19" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>114</v>
       </c>
-      <c r="C17" t="s">
+      <c r="B20" t="s">
         <v>115</v>
       </c>
-      <c r="D17" t="s">
+      <c r="C20" t="s">
         <v>116</v>
       </c>
-      <c r="E17" t="s">
+      <c r="D20" t="s">
         <v>117</v>
       </c>
-      <c r="F17" t="s">
+      <c r="E20" t="s">
         <v>118</v>
       </c>
-      <c r="G17" t="s">
+      <c r="F20" t="s">
         <v>119</v>
       </c>
-      <c r="H17" t="s">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="B21" t="s">
         <v>121</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C21" t="s">
         <v>122</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D21" t="s">
         <v>123</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E21" t="s">
         <v>124</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F21" t="s">
         <v>125</v>
       </c>
-      <c r="G18" t="s">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>126</v>
       </c>
-      <c r="H18" t="s">
+      <c r="B22" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C22" t="s">
         <v>128</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D22" t="s">
         <v>129</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E22" t="s">
         <v>130</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F22" t="s">
         <v>131</v>
       </c>
-      <c r="F19" t="s">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>132</v>
       </c>
-      <c r="G19" t="s">
+      <c r="B23" t="s">
         <v>133</v>
       </c>
-      <c r="H19" t="s">
+      <c r="C23" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="D23" t="s">
         <v>135</v>
       </c>
-      <c r="C20" t="s">
+      <c r="E23" t="s">
         <v>136</v>
       </c>
-      <c r="D20" t="s">
+      <c r="F23" t="s">
         <v>137</v>
       </c>
-      <c r="E20" t="s">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>138</v>
       </c>
-      <c r="F20" t="s">
+      <c r="B24" t="s">
         <v>139</v>
       </c>
-      <c r="G20" t="s">
+      <c r="C24" t="s">
         <v>140</v>
       </c>
-      <c r="H20" t="s">
+      <c r="D24" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="E24" t="s">
         <v>142</v>
       </c>
-      <c r="C21" t="s">
+      <c r="F24" t="s">
         <v>143</v>
       </c>
-      <c r="D21" t="s">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>144</v>
       </c>
-      <c r="E21" t="s">
+      <c r="B25" t="s">
         <v>145</v>
       </c>
-      <c r="F21" t="s">
+      <c r="C25" t="s">
         <v>146</v>
       </c>
-      <c r="G21" t="s">
+      <c r="D25" t="s">
+        <v>141</v>
+      </c>
+      <c r="E25" t="s">
         <v>147</v>
       </c>
-      <c r="H21" t="s">
+      <c r="F25" t="s">
         <v>148</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" t="s">
-        <v>149</v>
-      </c>
-      <c r="C22" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" t="s">
-        <v>151</v>
-      </c>
-      <c r="E22" t="s">
-        <v>152</v>
-      </c>
-      <c r="F22" t="s">
-        <v>146</v>
-      </c>
-      <c r="G22" t="s">
-        <v>153</v>
-      </c>
-      <c r="H22" t="s">
-        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/functional_tests/ZBIO-5213/ZBIO-5213.xlsx
+++ b/functional_tests/ZBIO-5213/ZBIO-5213.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="172">
   <si>
     <t>type</t>
   </si>
@@ -301,6 +301,87 @@
   </si>
   <si>
     <t>All communication channels display identical core information: same overdue amount, same due dates, same masked card number (****XXXX), same payment instructions, with only formatting differences appropriate to each channel's constraints.</t>
+  </si>
+  <si>
+    <t>Payment Plan Proposal - Customer Unable to Pay Full Balance</t>
+  </si>
+  <si>
+    <t>Verify that payment plan proposals are generated and sent to cardholders unable to pay full overdue balance with proper card identification.</t>
+  </si>
+  <si>
+    <t>TC-021</t>
+  </si>
+  <si>
+    <t>As a card issuer, I want to offer structured payment plans to cardholders who cannot pay their full overdue balance, providing them with manageable repayment options while maintaining proper account identification.</t>
+  </si>
+  <si>
+    <t>Credit card account with significant overdue balance, payment plan configuration system, reduced interest rate capabilities, cardholder communication system.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set up credit card account with high overdue balance ($5000+)
+2. Configure payment plan parameters (reduced interest rates, extended terms)
+3. Generate payment plan proposal for cardholder
+4. Verify proposal includes structured repayment schedule
+5. Check that last 4 digits of card number are included for identification
+6. Confirm reduced interest rates and fees are properly calculated
+7. Verify payment plan acceptance workflow</t>
+  </si>
+  <si>
+    <t>Payment plan proposal is sent containing: structured repayment schedule, reduced interest rates or waived fees, last 4 digits of card number for identification (****XXXX), clear terms and conditions, acceptance instructions, and customer service contact information for questions.</t>
+  </si>
+  <si>
+    <t>Collection Agency Involvement - Account Escalation</t>
+  </si>
+  <si>
+    <t>Verify that collection agency involvement is properly initiated with secure card identification when cardholders fail to respond to previous notifications.</t>
+  </si>
+  <si>
+    <t>TC-022</t>
+  </si>
+  <si>
+    <t>As a card issuer, I want to escalate severely delinquent accounts to collection agencies while ensuring only masked card information is shared for identification purposes.</t>
+  </si>
+  <si>
+    <t>Credit card account with 90+ days delinquency, previous collection notifications sent with no response, collection agency partnership configured, data transfer security protocols.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set up credit card account with 90+ days past due and no cardholder response
+2. Verify all previous collection notifications were sent and ignored
+3. Initiate collection agency transfer process
+4. Verify account data package includes only last 4 digits of card number
+5. Check that full card number is never transmitted to collection agency
+6. Confirm collection agency receives proper account identification data
+7. Verify cardholder is notified of collection agency involvement</t>
+  </si>
+  <si>
+    <t>Collection agency receives account information containing: total amount owed, payment history, contact information, last 4 digits of card number for identification (****XXXX), but never the full card number. Cardholder is notified of escalation with proper disclosure statements.</t>
+  </si>
+  <si>
+    <t>Legal Action Initiation - Extreme Delinquency Cases</t>
+  </si>
+  <si>
+    <t>Verify that legal action documentation includes proper card identification while maintaining security standards in extreme cases of non-payment.</t>
+  </si>
+  <si>
+    <t>TC-023</t>
+  </si>
+  <si>
+    <t>As a card issuer, I want to initiate legal action against severely delinquent cardholders while ensuring all legal documentation properly identifies the account using only masked card information.</t>
+  </si>
+  <si>
+    <t>Credit card account with 120+ days delinquency, failed collection efforts, legal department involvement, court document preparation system.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set up credit card account with 120+ days past due and failed collection attempts
+2. Initiate legal action preparation process
+3. Generate legal documentation and court filings
+4. Verify all legal documents include last 4 digits of card number for identification
+5. Confirm full card number is never included in legal documentation
+6. Check that court filings properly identify the account
+7. Verify cardholder notification of legal action includes masked card number</t>
+  </si>
+  <si>
+    <t>Legal documentation includes: account identification using last 4 digits of card number (****XXXX), total amount owed, payment history, collection efforts timeline, but never displays full card number. All court filings and legal notices maintain card data security standards.</t>
   </si>
   <si>
     <t>negative</t>
@@ -953,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1250,85 +1331,85 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
         <v>79</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>80</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>81</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>82</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>83</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>84</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>85</v>
-      </c>
-      <c r="H12" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
         <v>87</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>88</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>89</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>90</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>91</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>92</v>
-      </c>
-      <c r="H13" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" t="s">
         <v>94</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>95</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>96</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>97</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>98</v>
       </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
         <v>99</v>
-      </c>
-      <c r="H14" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="B15" t="s">
         <v>101</v>
@@ -1354,7 +1435,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="B16" t="s">
         <v>108</v>
@@ -1380,85 +1461,85 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" t="s">
         <v>115</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>116</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>117</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>118</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>119</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>120</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>121</v>
-      </c>
-      <c r="H17" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="B18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" t="s">
         <v>123</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>124</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>125</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>126</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>127</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>128</v>
-      </c>
-      <c r="H18" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" t="s">
         <v>130</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>131</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>132</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>133</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>134</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>135</v>
-      </c>
-      <c r="H19" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="B20" t="s">
         <v>137</v>
@@ -1484,7 +1565,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="B21" t="s">
         <v>144</v>
@@ -1506,6 +1587,84 @@
       </c>
       <c r="H21" t="s">
         <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" t="s">
+        <v>154</v>
+      </c>
+      <c r="F22" t="s">
+        <v>155</v>
+      </c>
+      <c r="G22" t="s">
+        <v>156</v>
+      </c>
+      <c r="H22" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" t="s">
+        <v>158</v>
+      </c>
+      <c r="C23" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" t="s">
+        <v>160</v>
+      </c>
+      <c r="E23" t="s">
+        <v>161</v>
+      </c>
+      <c r="F23" t="s">
+        <v>162</v>
+      </c>
+      <c r="G23" t="s">
+        <v>163</v>
+      </c>
+      <c r="H23" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" t="s">
+        <v>167</v>
+      </c>
+      <c r="E24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F24" t="s">
+        <v>169</v>
+      </c>
+      <c r="G24" t="s">
+        <v>170</v>
+      </c>
+      <c r="H24" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/functional_tests/ZBIO-5213/ZBIO-5213.xlsx
+++ b/functional_tests/ZBIO-5213/ZBIO-5213.xlsx
@@ -4,22 +4,16 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Test Scenarios" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="151">
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>description</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+  <si>
+    <t>scenario</t>
   </si>
   <si>
     <t>testId</t>
@@ -37,13 +31,7 @@
     <t>expectedResult</t>
   </si>
   <si>
-    <t>functional</t>
-  </si>
-  <si>
-    <t>Credit Card Payment Reminder Notification - Happy Path</t>
-  </si>
-  <si>
-    <t>Verify that cardholders receive automated payment due reminders before their payment due date with masked card details.</t>
+    <t>&lt;Credit Card Payment Reminder Notification - Happy Path-Verify that cardholders receive automated payment due reminders before their payment due date with masked card details.&gt;</t>
   </si>
   <si>
     <t>TC-001</t>
@@ -65,10 +53,7 @@
     <t>Cardholder receives payment reminder notification containing: due date, minimum payment amount, last 4 digits of card number (e.g., ****1234), payment options, and clear call-to-action. Full card number is never displayed.</t>
   </si>
   <si>
-    <t>Overdue Balance Alert - First Alert</t>
-  </si>
-  <si>
-    <t>Verify that cardholders receive immediate overdue balance alerts when payment due date is missed.</t>
+    <t>&lt;Overdue Balance Alert - First Alert-Verify that cardholders receive immediate overdue balance alerts when payment due date is missed.&gt;</t>
   </si>
   <si>
     <t>TC-002</t>
@@ -90,10 +75,7 @@
     <t>Cardholder receives overdue balance alert within 24 hours of missed due date containing: overdue amount, late fee information, last 4 digits of card number, consequences of continued non-payment, payment instructions, and customer service contact information.</t>
   </si>
   <si>
-    <t>Collection Notification - Escalated Delinquency</t>
-  </si>
-  <si>
-    <t>Verify that formal collection notifications are sent when accounts become significantly delinquent.</t>
+    <t>&lt;Collection Notification - Escalated Delinquency-Verify that formal collection notifications are sent when accounts become significantly delinquent.&gt;</t>
   </si>
   <si>
     <t>TC-003</t>
@@ -116,10 +98,7 @@
     <t>Formal collection notification is sent containing: total amount owed, breakdown of principal and fees, last 4 digits of card number, legal consequences of non-payment, payment deadline, dispute rights, collection agency contact information, and regulatory compliance statements.</t>
   </si>
   <si>
-    <t>Multiple Card Numbers - Correct Masking</t>
-  </si>
-  <si>
-    <t>Verify that cardholders with multiple credit cards receive notifications with correctly masked card numbers for the specific delinquent account.</t>
+    <t>&lt;Multiple Card Numbers - Correct Masking-Verify that cardholders with multiple credit cards receive notifications with correctly masked card numbers for the specific delinquent account.&gt;</t>
   </si>
   <si>
     <t>TC-004</t>
@@ -142,10 +121,7 @@
     <t>Notification correctly identifies the delinquent card account using only the last 4 digits of the specific overdue card, preventing confusion with other active cards on the same customer profile.</t>
   </si>
   <si>
-    <t>Card Number Security - No Full Number Exposure</t>
-  </si>
-  <si>
-    <t>Verify that full credit card numbers are never displayed in any collection lifecycle communications.</t>
+    <t>&lt;Card Number Security - No Full Number Exposure-Verify that full credit card numbers are never displayed in any collection lifecycle communications.&gt;</t>
   </si>
   <si>
     <t>TC-005</t>
@@ -168,10 +144,7 @@
     <t>All collection communications show only masked card numbers (****XXXX format), full 16-digit card numbers are never visible in plain text, system logs show encrypted card data only, and PCI DSS compliance is maintained.</t>
   </si>
   <si>
-    <t>Progressive Collection Escalation Workflow</t>
-  </si>
-  <si>
-    <t>Verify that the collection lifecycle progresses through all stages with appropriate timing and escalation.</t>
+    <t>&lt;Progressive Collection Escalation Workflow-Verify that the collection lifecycle progresses through all stages with appropriate timing and escalation.&gt;</t>
   </si>
   <si>
     <t>TC-006</t>
@@ -196,10 +169,7 @@
     <t>Collection workflow executes in proper sequence: payment reminder (before due date) → overdue alert (day 1) → escalated alert (day 30) → formal collection notice (day 60), with each communication appropriately escalating in tone and consequences while maintaining card number masking.</t>
   </si>
   <si>
-    <t>Customer Response to Collection Notifications</t>
-  </si>
-  <si>
-    <t>Verify that collection workflow appropriately responds when customers make payments or contact customer service.</t>
+    <t>&lt;Customer Response to Collection Notifications-Verify that collection workflow appropriately responds when customers make payments or contact customer service.&gt;</t>
   </si>
   <si>
     <t>TC-007</t>
@@ -223,10 +193,7 @@
     <t>Collection workflow dynamically adjusts: partial payments trigger modified collection notices with updated balances, payment arrangements pause automatic collections, customer service interactions are logged and affect workflow, full payments immediately stop all collection activities.</t>
   </si>
   <si>
-    <t>Invalid or Missing Contact Information</t>
-  </si>
-  <si>
-    <t>Verify system behavior when cardholders have invalid or missing contact information during collection lifecycle.</t>
+    <t>&lt;Invalid or Missing Contact Information-Verify system behavior when cardholders have invalid or missing contact information during collection lifecycle.&gt;</t>
   </si>
   <si>
     <t>TC-008</t>
@@ -250,10 +217,7 @@
     <t>System gracefully handles communication failures: bounced emails trigger SMS or postal mail, disconnected SMS triggers email or postal mail, failed electronic communications escalate to physical mail with last 4 digits of card number, all failed attempts are logged for compliance.</t>
   </si>
   <si>
-    <t>Regulatory Compliance in Collection Notices</t>
-  </si>
-  <si>
-    <t>Verify that all collection communications comply with relevant consumer protection and debt collection regulations.</t>
+    <t>&lt;Regulatory Compliance in Collection Notices-Verify that all collection communications comply with relevant consumer protection and debt collection regulations.&gt;</t>
   </si>
   <si>
     <t>TC-009</t>
@@ -277,10 +241,7 @@
     <t>All collection communications include: required legal disclosures, dispute rights information, opt-out instructions, appropriate contact information, last 4 digits of card number for identification, compliant language and tone, and adherence to timing restrictions for consumer contact.</t>
   </si>
   <si>
-    <t>Cross-Channel Notification Consistency</t>
-  </si>
-  <si>
-    <t>Verify that collection notifications maintain consistent information across all communication channels.</t>
+    <t>&lt;Cross-Channel Notification Consistency-Verify that collection notifications maintain consistent information across all communication channels.&gt;</t>
   </si>
   <si>
     <t>TC-010</t>
@@ -303,13 +264,79 @@
     <t>All communication channels display identical core information: same overdue amount, same due dates, same masked card number (****XXXX), same payment instructions, with only formatting differences appropriate to each channel's constraints.</t>
   </si>
   <si>
-    <t>negative</t>
-  </si>
-  <si>
-    <t>System Failure During Critical Collection Period</t>
-  </si>
-  <si>
-    <t>Verify system behavior when notification services fail during critical collection periods.</t>
+    <t>&lt;Payment Plan Proposal - Customer Unable to Pay Full Balance-Verify that payment plan proposals are generated and sent to cardholders unable to pay full overdue balance with proper card identification.&gt;</t>
+  </si>
+  <si>
+    <t>TC-021</t>
+  </si>
+  <si>
+    <t>As a card issuer, I want to offer structured payment plans to cardholders who cannot pay their full overdue balance, providing them with manageable repayment options while maintaining proper account identification.</t>
+  </si>
+  <si>
+    <t>Credit card account with significant overdue balance, payment plan configuration system, reduced interest rate capabilities, cardholder communication system.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set up credit card account with high overdue balance ($5000+)
+2. Configure payment plan parameters (reduced interest rates, extended terms)
+3. Generate payment plan proposal for cardholder
+4. Verify proposal includes structured repayment schedule
+5. Check that last 4 digits of card number are included for identification
+6. Confirm reduced interest rates and fees are properly calculated
+7. Verify payment plan acceptance workflow</t>
+  </si>
+  <si>
+    <t>Payment plan proposal is sent containing: structured repayment schedule, reduced interest rates or waived fees, last 4 digits of card number for identification (****XXXX), clear terms and conditions, acceptance instructions, and customer service contact information for questions.</t>
+  </si>
+  <si>
+    <t>&lt;Collection Agency Involvement - Account Escalation-Verify that collection agency involvement is properly initiated with secure card identification when cardholders fail to respond to previous notifications.&gt;</t>
+  </si>
+  <si>
+    <t>TC-022</t>
+  </si>
+  <si>
+    <t>As a card issuer, I want to escalate severely delinquent accounts to collection agencies while ensuring only masked card information is shared for identification purposes.</t>
+  </si>
+  <si>
+    <t>Credit card account with 90+ days delinquency, previous collection notifications sent with no response, collection agency partnership configured, data transfer security protocols.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set up credit card account with 90+ days past due and no cardholder response
+2. Verify all previous collection notifications were sent and ignored
+3. Initiate collection agency transfer process
+4. Verify account data package includes only last 4 digits of card number
+5. Check that full card number is never transmitted to collection agency
+6. Confirm collection agency receives proper account identification data
+7. Verify cardholder is notified of collection agency involvement</t>
+  </si>
+  <si>
+    <t>Collection agency receives account information containing: total amount owed, payment history, contact information, last 4 digits of card number for identification (****XXXX), but never the full card number. Cardholder is notified of escalation with proper disclosure statements.</t>
+  </si>
+  <si>
+    <t>&lt;Legal Action Initiation - Extreme Delinquency Cases-Verify that legal action documentation includes proper card identification while maintaining security standards in extreme cases of non-payment.&gt;</t>
+  </si>
+  <si>
+    <t>TC-023</t>
+  </si>
+  <si>
+    <t>As a card issuer, I want to initiate legal action against severely delinquent cardholders while ensuring all legal documentation properly identifies the account using only masked card information.</t>
+  </si>
+  <si>
+    <t>Credit card account with 120+ days delinquency, failed collection efforts, legal department involvement, court document preparation system.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set up credit card account with 120+ days past due and failed collection attempts
+2. Initiate legal action preparation process
+3. Generate legal documentation and court filings
+4. Verify all legal documents include last 4 digits of card number for identification
+5. Confirm full card number is never included in legal documentation
+6. Check that court filings properly identify the account
+7. Verify cardholder notification of legal action includes masked card number</t>
+  </si>
+  <si>
+    <t>Legal documentation includes: account identification using last 4 digits of card number (****XXXX), total amount owed, payment history, collection efforts timeline, but never displays full card number. All court filings and legal notices maintain card data security standards.</t>
+  </si>
+  <si>
+    <t>&lt;System Failure During Critical Collection Period-Verify system behavior when notification services fail during critical collection periods.&gt;</t>
   </si>
   <si>
     <t>TC-011</t>
@@ -333,10 +360,7 @@
     <t>System maintains collection workflow continuity: failed email notifications trigger SMS backup, complete electronic failure triggers postal mail, notification queue preserves pending messages, system recovery resends failed notifications, audit trail tracks all failures and recoveries.</t>
   </si>
   <si>
-    <t>Invalid Card Data in Collection System</t>
-  </si>
-  <si>
-    <t>Verify system behavior when card data becomes corrupted or invalid during collection lifecycle.</t>
+    <t>&lt;Invalid Card Data in Collection System-Verify system behavior when card data becomes corrupted or invalid during collection lifecycle.&gt;</t>
   </si>
   <si>
     <t>TC-012</t>
@@ -360,10 +384,7 @@
     <t>System gracefully handles invalid card data: missing last 4 digits trigger account lookup by other identifiers, corrupted data generates error alerts to operations team, notifications include generic account identifiers when card masking fails, system never displays corrupted card data to customers.</t>
   </si>
   <si>
-    <t>Duplicate Collection Notifications</t>
-  </si>
-  <si>
-    <t>Verify system prevents sending duplicate collection notifications to cardholders.</t>
+    <t>&lt;Duplicate Collection Notifications-Verify system prevents sending duplicate collection notifications to cardholders.&gt;</t>
   </si>
   <si>
     <t>TC-013</t>
@@ -387,10 +408,7 @@
     <t>System prevents duplicate notifications: only one notification per type per day, concurrent triggers are deduplicated, system restart doesn't cause resending, different notification types (reminder vs overdue) can be sent same day, audit log shows all trigger attempts but only successful sends.</t>
   </si>
   <si>
-    <t>Collection Notification with Zero Balance</t>
-  </si>
-  <si>
-    <t>Verify system behavior when attempting to send collection notifications for accounts with zero or negative balances.</t>
+    <t>&lt;Collection Notification with Zero Balance-Verify system behavior when attempting to send collection notifications for accounts with zero or negative balances.&gt;</t>
   </si>
   <si>
     <t>TC-014</t>
@@ -414,10 +432,7 @@
     <t>System prevents inappropriate collection communications: zero balance accounts don't receive collection notices, credit balance accounts are excluded from collection workflow, payment processing immediately updates collection eligibility, scheduled notifications are cancelled when balance is resolved.</t>
   </si>
   <si>
-    <t>Malformed Contact Information in Collection Database</t>
-  </si>
-  <si>
-    <t>Verify system handling of malformed or invalid contact information during collection notification attempts.</t>
+    <t>&lt;Malformed Contact Information in Collection Database-Verify system handling of malformed or invalid contact information during collection notification attempts.&gt;</t>
   </si>
   <si>
     <t>TC-015</t>
@@ -441,13 +456,7 @@
     <t>System handles malformed contact data gracefully: invalid emails are rejected and backup SMS is attempted, malformed phone numbers trigger email backup, completely invalid contact data escalates to postal mail, error logs capture all validation failures, customer service receives alerts for contact data correction.</t>
   </si>
   <si>
-    <t>non-functional</t>
-  </si>
-  <si>
-    <t>Collection Notification Performance Under High Load</t>
-  </si>
-  <si>
-    <t>Verify system performance when processing large volumes of collection notifications simultaneously.</t>
+    <t>&lt;Collection Notification Performance Under High Load-Verify system performance when processing large volumes of collection notifications simultaneously.&gt;</t>
   </si>
   <si>
     <t>TC-016</t>
@@ -471,10 +480,7 @@
     <t>System maintains performance under load: processes minimum 100 notifications per minute, database response times remain under 2 seconds, notification delivery completes within 4 hours for large batches, system resource utilization stays below 80%, no notification failures due to load, proper masking of card numbers maintained at scale.</t>
   </si>
   <si>
-    <t>Collection System Security and Data Protection</t>
-  </si>
-  <si>
-    <t>Verify security measures and data protection in collection notification system.</t>
+    <t>&lt;Collection System Security and Data Protection-Verify security measures and data protection in collection notification system.&gt;</t>
   </si>
   <si>
     <t>TC-017</t>
@@ -498,10 +504,7 @@
     <t>System maintains high security standards: all card data encrypted with AES-256, TLS 1.3 for data in transit, role-based access controls enforced, comprehensive audit logging active, full card numbers never appear in plain text, secure deletion procedures followed, PCI DSS compliance maintained.</t>
   </si>
   <si>
-    <t>Collection Notification System Reliability</t>
-  </si>
-  <si>
-    <t>Verify system reliability and uptime for collection notification services.</t>
+    <t>&lt;Collection Notification System Reliability-Verify system reliability and uptime for collection notification services.&gt;</t>
   </si>
   <si>
     <t>TC-018</t>
@@ -525,10 +528,7 @@
     <t>System demonstrates high reliability: 99.9% uptime maintained, automatic failover completes within 30 seconds, no data loss during failover events, notification queues preserved during outages, system recovery doesn't cause duplicate notifications, consistent card number masking maintained through all failure scenarios.</t>
   </si>
   <si>
-    <t>Collection Notification Accessibility Compliance</t>
-  </si>
-  <si>
-    <t>Verify that collection notifications are accessible to cardholders with disabilities.</t>
+    <t>&lt;Collection Notification Accessibility Compliance-Verify that collection notifications are accessible to cardholders with disabilities.&gt;</t>
   </si>
   <si>
     <t>TC-019</t>
@@ -552,10 +552,7 @@
     <t>Collection notifications meet accessibility standards: screen readers properly announce card masking (****1234), proper heading hierarchy used, minimum 4.5:1 color contrast ratio maintained, keyboard navigation fully functional, alternative text provided for images, font sizes minimum 14pt, WCAG 2.1 AA compliance achieved.</t>
   </si>
   <si>
-    <t>Multi-Language Collection Notification Support</t>
-  </si>
-  <si>
-    <t>Verify that collection notifications support multiple languages while maintaining card number security.</t>
+    <t>&lt;Multi-Language Collection Notification Support-Verify that collection notifications support multiple languages while maintaining card number security.&gt;</t>
   </si>
   <si>
     <t>TC-020</t>
@@ -953,16 +950,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19" customWidth="1"/>
-    <col min="2" max="3" width="50" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="5" max="8" width="50" customWidth="1"/>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="6" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -981,531 +977,465 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B3" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
+      <c r="D3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
+      <c r="D4" t="s">
         <v>21</v>
       </c>
-      <c r="H3" t="s">
+      <c r="E4" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="F4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="E4" t="s">
+      <c r="C5" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
+      <c r="D5" t="s">
         <v>27</v>
       </c>
-      <c r="G4" t="s">
+      <c r="E5" t="s">
         <v>28</v>
       </c>
-      <c r="H4" t="s">
+      <c r="F5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>30</v>
       </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
         <v>31</v>
       </c>
-      <c r="D5" t="s">
+      <c r="C6" t="s">
         <v>32</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D6" t="s">
         <v>33</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E6" t="s">
         <v>34</v>
       </c>
-      <c r="G5" t="s">
+      <c r="F6" t="s">
         <v>35</v>
       </c>
-      <c r="H5" t="s">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="B7" t="s">
         <v>37</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>38</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>39</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
         <v>40</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F7" t="s">
         <v>41</v>
       </c>
-      <c r="G6" t="s">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>42</v>
       </c>
-      <c r="H6" t="s">
+      <c r="B8" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C8" t="s">
         <v>44</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D8" t="s">
         <v>45</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E8" t="s">
         <v>46</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F8" t="s">
         <v>47</v>
       </c>
-      <c r="F7" t="s">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>48</v>
       </c>
-      <c r="G7" t="s">
+      <c r="B9" t="s">
         <v>49</v>
       </c>
-      <c r="H7" t="s">
+      <c r="C9" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="D9" t="s">
         <v>51</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E9" t="s">
         <v>52</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F9" t="s">
         <v>53</v>
       </c>
-      <c r="E8" t="s">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>54</v>
       </c>
-      <c r="F8" t="s">
+      <c r="B10" t="s">
         <v>55</v>
       </c>
-      <c r="G8" t="s">
+      <c r="C10" t="s">
         <v>56</v>
       </c>
-      <c r="H8" t="s">
+      <c r="D10" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="E10" t="s">
         <v>58</v>
       </c>
-      <c r="C9" t="s">
+      <c r="F10" t="s">
         <v>59</v>
       </c>
-      <c r="D9" t="s">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>60</v>
       </c>
-      <c r="E9" t="s">
+      <c r="B11" t="s">
         <v>61</v>
       </c>
-      <c r="F9" t="s">
+      <c r="C11" t="s">
         <v>62</v>
       </c>
-      <c r="G9" t="s">
+      <c r="D11" t="s">
         <v>63</v>
       </c>
-      <c r="H9" t="s">
+      <c r="E11" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="F11" t="s">
         <v>65</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>66</v>
       </c>
-      <c r="D10" t="s">
+      <c r="B12" t="s">
         <v>67</v>
       </c>
-      <c r="E10" t="s">
+      <c r="C12" t="s">
         <v>68</v>
       </c>
-      <c r="F10" t="s">
+      <c r="D12" t="s">
         <v>69</v>
       </c>
-      <c r="G10" t="s">
+      <c r="E12" t="s">
         <v>70</v>
       </c>
-      <c r="H10" t="s">
+      <c r="F12" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>72</v>
       </c>
-      <c r="C11" t="s">
+      <c r="B13" t="s">
         <v>73</v>
       </c>
-      <c r="D11" t="s">
+      <c r="C13" t="s">
         <v>74</v>
       </c>
-      <c r="E11" t="s">
+      <c r="D13" t="s">
         <v>75</v>
       </c>
-      <c r="F11" t="s">
+      <c r="E13" t="s">
         <v>76</v>
       </c>
-      <c r="G11" t="s">
+      <c r="F13" t="s">
         <v>77</v>
       </c>
-      <c r="H11" t="s">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="B14" t="s">
         <v>79</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C14" t="s">
         <v>80</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D14" t="s">
         <v>81</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E14" t="s">
         <v>82</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F14" t="s">
         <v>83</v>
       </c>
-      <c r="F12" t="s">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>84</v>
       </c>
-      <c r="G12" t="s">
+      <c r="B15" t="s">
         <v>85</v>
       </c>
-      <c r="H12" t="s">
+      <c r="C15" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="D15" t="s">
         <v>87</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E15" t="s">
         <v>88</v>
       </c>
-      <c r="D13" t="s">
+      <c r="F15" t="s">
         <v>89</v>
       </c>
-      <c r="E13" t="s">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>90</v>
       </c>
-      <c r="F13" t="s">
+      <c r="B16" t="s">
         <v>91</v>
       </c>
-      <c r="G13" t="s">
+      <c r="C16" t="s">
         <v>92</v>
       </c>
-      <c r="H13" t="s">
+      <c r="D16" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="E16" t="s">
         <v>94</v>
       </c>
-      <c r="C14" t="s">
+      <c r="F16" t="s">
         <v>95</v>
       </c>
-      <c r="D14" t="s">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>96</v>
       </c>
-      <c r="E14" t="s">
+      <c r="B17" t="s">
         <v>97</v>
       </c>
-      <c r="F14" t="s">
+      <c r="C17" t="s">
         <v>98</v>
       </c>
-      <c r="G14" t="s">
+      <c r="D17" t="s">
         <v>99</v>
       </c>
-      <c r="H14" t="s">
+      <c r="E17" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>79</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="F17" t="s">
         <v>101</v>
       </c>
-      <c r="C15" t="s">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>102</v>
       </c>
-      <c r="D15" t="s">
+      <c r="B18" t="s">
         <v>103</v>
       </c>
-      <c r="E15" t="s">
+      <c r="C18" t="s">
         <v>104</v>
       </c>
-      <c r="F15" t="s">
+      <c r="D18" t="s">
         <v>105</v>
       </c>
-      <c r="G15" t="s">
+      <c r="E18" t="s">
         <v>106</v>
       </c>
-      <c r="H15" t="s">
+      <c r="F18" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>108</v>
       </c>
-      <c r="C16" t="s">
+      <c r="B19" t="s">
         <v>109</v>
       </c>
-      <c r="D16" t="s">
+      <c r="C19" t="s">
         <v>110</v>
       </c>
-      <c r="E16" t="s">
+      <c r="D19" t="s">
         <v>111</v>
       </c>
-      <c r="F16" t="s">
+      <c r="E19" t="s">
         <v>112</v>
       </c>
-      <c r="G16" t="s">
+      <c r="F19" t="s">
         <v>113</v>
       </c>
-      <c r="H16" t="s">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B20" t="s">
         <v>115</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C20" t="s">
         <v>116</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D20" t="s">
         <v>117</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E20" t="s">
         <v>118</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F20" t="s">
         <v>119</v>
       </c>
-      <c r="F17" t="s">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>120</v>
       </c>
-      <c r="G17" t="s">
+      <c r="B21" t="s">
         <v>121</v>
       </c>
-      <c r="H17" t="s">
+      <c r="C21" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="D21" t="s">
         <v>123</v>
       </c>
-      <c r="C18" t="s">
+      <c r="E21" t="s">
         <v>124</v>
       </c>
-      <c r="D18" t="s">
+      <c r="F21" t="s">
         <v>125</v>
       </c>
-      <c r="E18" t="s">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>126</v>
       </c>
-      <c r="F18" t="s">
+      <c r="B22" t="s">
         <v>127</v>
       </c>
-      <c r="G18" t="s">
+      <c r="C22" t="s">
         <v>128</v>
       </c>
-      <c r="H18" t="s">
+      <c r="D22" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>115</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="E22" t="s">
         <v>130</v>
       </c>
-      <c r="C19" t="s">
+      <c r="F22" t="s">
         <v>131</v>
       </c>
-      <c r="D19" t="s">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>132</v>
       </c>
-      <c r="E19" t="s">
+      <c r="B23" t="s">
         <v>133</v>
       </c>
-      <c r="F19" t="s">
+      <c r="C23" t="s">
         <v>134</v>
       </c>
-      <c r="G19" t="s">
+      <c r="D23" t="s">
         <v>135</v>
       </c>
-      <c r="H19" t="s">
+      <c r="E23" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>115</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="F23" t="s">
         <v>137</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>138</v>
       </c>
-      <c r="D20" t="s">
+      <c r="B24" t="s">
         <v>139</v>
       </c>
-      <c r="E20" t="s">
+      <c r="C24" t="s">
         <v>140</v>
       </c>
-      <c r="F20" t="s">
+      <c r="D24" t="s">
         <v>141</v>
       </c>
-      <c r="G20" t="s">
+      <c r="E24" t="s">
         <v>142</v>
       </c>
-      <c r="H20" t="s">
+      <c r="F24" t="s">
         <v>143</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" t="s">
-        <v>144</v>
-      </c>
-      <c r="C21" t="s">
-        <v>145</v>
-      </c>
-      <c r="D21" t="s">
-        <v>146</v>
-      </c>
-      <c r="E21" t="s">
-        <v>147</v>
-      </c>
-      <c r="F21" t="s">
-        <v>148</v>
-      </c>
-      <c r="G21" t="s">
-        <v>149</v>
-      </c>
-      <c r="H21" t="s">
-        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/functional_tests/ZBIO-5213/ZBIO-5213.xlsx
+++ b/functional_tests/ZBIO-5213/ZBIO-5213.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="172">
   <si>
     <t>type</t>
   </si>
@@ -303,6 +303,33 @@
     <t>All communication channels display identical core information: same overdue amount, same due dates, same masked card number (****XXXX), same payment instructions, with only formatting differences appropriate to each channel's constraints.</t>
   </si>
   <si>
+    <t>Excel Report Generation for Collection Data</t>
+  </si>
+  <si>
+    <t>Verify that collection managers can generate Excel reports containing masked card numbers and collection status information.</t>
+  </si>
+  <si>
+    <t>TC-021</t>
+  </si>
+  <si>
+    <t>As a collection manager, I want to generate Excel reports with delinquent account information so that I can analyze collection performance and track account statuses while maintaining card security.</t>
+  </si>
+  <si>
+    <t>Collection management system with reporting capability, multiple overdue credit card accounts at various delinquency stages, Excel export functionality configured.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set up multiple overdue credit card accounts (30, 60, 90+ days past due)
+2. Access collection reporting dashboard
+3. Select Excel export option for delinquent accounts
+4. Configure report parameters (date range, delinquency stage, balance thresholds)
+5. Generate and download Excel file
+6. Verify Excel file contents and formatting
+7. Check card number masking in exported data</t>
+  </si>
+  <si>
+    <t>Excel report is successfully generated containing: account identifiers, last 4 digits of card numbers (****XXXX format), delinquency stages, outstanding balances, last payment dates, collection actions taken, and contact attempt history. Full card numbers are never exposed in the Excel file.</t>
+  </si>
+  <si>
     <t>negative</t>
   </si>
   <si>
@@ -441,6 +468,34 @@
     <t>System handles malformed contact data gracefully: invalid emails are rejected and backup SMS is attempted, malformed phone numbers trigger email backup, completely invalid contact data escalates to postal mail, error logs capture all validation failures, customer service receives alerts for contact data correction.</t>
   </si>
   <si>
+    <t>Excel Export Failure During Report Generation</t>
+  </si>
+  <si>
+    <t>Verify system behavior when Excel export functionality fails during collection report generation.</t>
+  </si>
+  <si>
+    <t>TC-022</t>
+  </si>
+  <si>
+    <t>Test system handling of Excel export failures and error recovery mechanisms during collection reporting.</t>
+  </si>
+  <si>
+    <t>Collection reporting system with Excel export capability, large dataset of collection accounts, ability to simulate export failures.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set up collection report with large dataset (1000+ accounts)
+2. Initiate Excel export process
+3. Simulate disk space shortage during export
+4. Verify error handling and user notification
+5. Test with memory limitations during large exports
+6. Simulate network interruption during download
+7. Check system recovery and retry mechanisms
+8. Verify no partial or corrupted Excel files are delivered</t>
+  </si>
+  <si>
+    <t>System handles Excel export failures gracefully: disk space errors display clear error messages, memory limitations trigger alternative export methods, network interruptions allow download retry, failed exports don't create corrupted files, error logs capture all failure details, users receive appropriate feedback on export status.</t>
+  </si>
+  <si>
     <t>non-functional</t>
   </si>
   <si>
@@ -577,6 +632,33 @@
   </si>
   <si>
     <t>Multi-language support maintains security and compliance: card masking format (****XXXX) consistent across all languages, regulatory disclosures accurately translated, currency and date formats localized correctly, contact information provided in appropriate language, legal compliance maintained for each jurisdiction, character encoding supports all languages properly.</t>
+  </si>
+  <si>
+    <t>Excel Report Generation Performance</t>
+  </si>
+  <si>
+    <t>Verify performance and scalability of Excel report generation for collection data.</t>
+  </si>
+  <si>
+    <t>TC-023</t>
+  </si>
+  <si>
+    <t>Test system performance when generating large Excel reports with thousands of collection records while maintaining card security.</t>
+  </si>
+  <si>
+    <t>Large collection dataset (50,000+ accounts), performance monitoring tools, Excel generation system, baseline performance metrics.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Set up collection dataset with 50,000 delinquent accounts
+2. Initiate Excel report generation for full dataset
+3. Monitor system resource utilization during export
+4. Measure report generation time and file size
+5. Test concurrent Excel report requests from multiple users
+6. Verify card number masking performance at scale
+7. Check memory usage and cleanup after report generation</t>
+  </si>
+  <si>
+    <t>Excel report generation maintains performance: generates reports with 50,000+ records within 5 minutes, memory usage stays below 2GB during generation, concurrent requests don't degrade performance significantly, card masking processing adds less than 10% overhead, temporary files are properly cleaned up, system resources return to baseline after completion.</t>
   </si>
 </sst>
 </file>
@@ -953,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1250,33 +1332,33 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
         <v>79</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>80</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>81</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>82</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>83</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>84</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>85</v>
-      </c>
-      <c r="H12" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
         <v>87</v>
@@ -1302,7 +1384,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
         <v>94</v>
@@ -1328,7 +1410,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
         <v>101</v>
@@ -1354,7 +1436,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
         <v>108</v>
@@ -1380,59 +1462,59 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
         <v>115</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>116</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>117</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>118</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>119</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>120</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
         <v>121</v>
-      </c>
-      <c r="H17" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" t="s">
         <v>123</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>124</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>125</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>126</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>127</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>128</v>
-      </c>
-      <c r="H18" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s">
         <v>130</v>
@@ -1458,7 +1540,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="B20" t="s">
         <v>137</v>
@@ -1484,7 +1566,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="B21" t="s">
         <v>144</v>
@@ -1506,6 +1588,84 @@
       </c>
       <c r="H21" t="s">
         <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>129</v>
+      </c>
+      <c r="B22" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" t="s">
+        <v>152</v>
+      </c>
+      <c r="D22" t="s">
+        <v>153</v>
+      </c>
+      <c r="E22" t="s">
+        <v>154</v>
+      </c>
+      <c r="F22" t="s">
+        <v>155</v>
+      </c>
+      <c r="G22" t="s">
+        <v>156</v>
+      </c>
+      <c r="H22" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" t="s">
+        <v>158</v>
+      </c>
+      <c r="C23" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" t="s">
+        <v>160</v>
+      </c>
+      <c r="E23" t="s">
+        <v>161</v>
+      </c>
+      <c r="F23" t="s">
+        <v>162</v>
+      </c>
+      <c r="G23" t="s">
+        <v>163</v>
+      </c>
+      <c r="H23" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" t="s">
+        <v>165</v>
+      </c>
+      <c r="C24" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" t="s">
+        <v>167</v>
+      </c>
+      <c r="E24" t="s">
+        <v>168</v>
+      </c>
+      <c r="F24" t="s">
+        <v>169</v>
+      </c>
+      <c r="G24" t="s">
+        <v>170</v>
+      </c>
+      <c r="H24" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>
